--- a/docs/schema/DB設計 テーブル定義書.xlsx
+++ b/docs/schema/DB設計 テーブル定義書.xlsx
@@ -1,37 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3030846\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F74BB54-3E0A-4095-B917-4F3BA5C1615D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F9B21C-C12F-46EF-A9C7-4AD8E8D75CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
-    <sheet name="目次・概要" sheetId="2" r:id="rId2"/>
-    <sheet name="authentications" sheetId="5" r:id="rId3"/>
-    <sheet name="answer_patterns" sheetId="12" r:id="rId4"/>
-    <sheet name="answer_pattern_items" sheetId="13" r:id="rId5"/>
-    <sheet name="questions" sheetId="4" r:id="rId6"/>
-    <sheet name="responses" sheetId="7" r:id="rId7"/>
-    <sheet name="response_details" sheetId="8" r:id="rId8"/>
-    <sheet name="surveys" sheetId="3" r:id="rId9"/>
-    <sheet name="survey_target_groups" sheetId="11" r:id="rId10"/>
-    <sheet name="user_groups" sheetId="9" r:id="rId11"/>
-    <sheet name="user_group_mappings" sheetId="10" r:id="rId12"/>
+    <sheet name="更新履歴" sheetId="14" r:id="rId2"/>
+    <sheet name="目次・概要" sheetId="2" r:id="rId3"/>
+    <sheet name="authentications" sheetId="5" r:id="rId4"/>
+    <sheet name="answer_patterns" sheetId="12" r:id="rId5"/>
+    <sheet name="answer_pattern_items" sheetId="13" r:id="rId6"/>
+    <sheet name="questions" sheetId="4" r:id="rId7"/>
+    <sheet name="responses" sheetId="7" r:id="rId8"/>
+    <sheet name="response_details" sheetId="8" r:id="rId9"/>
+    <sheet name="surveys" sheetId="3" r:id="rId10"/>
+    <sheet name="survey_target_groups" sheetId="11" r:id="rId11"/>
+    <sheet name="user_groups" sheetId="9" r:id="rId12"/>
+    <sheet name="user_group_mappings" sheetId="10" r:id="rId13"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId14"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="範囲１" localSheetId="1">#REF!</definedName>
+    <definedName name="範囲１">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="177">
   <si>
     <t>テーブル定義書</t>
   </si>
@@ -306,6 +314,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 CREATE TABLE authentications (
@@ -539,6 +548,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>(~</t>
     </r>
@@ -557,6 +567,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -576,6 +587,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
         status response_status NOT NULL DEFAULT 'UNVERIFIED',
@@ -751,6 +763,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
         answer_text text
@@ -772,6 +785,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>status survey_status NOT NULL DEFAULT 'DRAFT',
         result_visibility result_visibility NOT NULL DEFAULT 'ADMIN_ONLY',
@@ -1119,12 +1133,54 @@
     </rPh>
     <phoneticPr fontId="11"/>
   </si>
+  <si>
+    <t>外部設計書</t>
+    <rPh sb="0" eb="4">
+      <t>ガイブセッケイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="27"/>
+  </si>
+  <si>
+    <t>更新履歴</t>
+  </si>
+  <si>
+    <t>作成・更新日</t>
+  </si>
+  <si>
+    <t>更新者</t>
+  </si>
+  <si>
+    <t>更新箇所</t>
+  </si>
+  <si>
+    <t>更新内容</t>
+  </si>
+  <si>
+    <t>初版</t>
+    <rPh sb="0" eb="2">
+      <t>ショバン</t>
+    </rPh>
+    <phoneticPr fontId="27"/>
+  </si>
+  <si>
+    <t>全体</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンタイ</t>
+    </rPh>
+    <phoneticPr fontId="27"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
+  </numFmts>
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1135,56 +1191,66 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1283,8 +1349,47 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1309,8 +1414,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1450,12 +1561,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1533,6 +1697,17 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1544,53 +1719,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1603,15 +1739,93 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準_生産計画ED書" xfId="2" xr:uid="{936C50A2-657D-45DD-8AC5-EBAD03876189}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1678,6 +1892,34 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="表紙"/>
+      <sheetName val="更新履歴"/>
+      <sheetName val="システム構成"/>
+      <sheetName val="レイヤ―構成"/>
+      <sheetName val="機能一覧"/>
+      <sheetName val="画面一覧"/>
+      <sheetName val="画面遷移図"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1929,34 +2171,34 @@
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="4"/>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="41"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="48"/>
       <c r="K10" s="5"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="4"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="44"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="51"/>
       <c r="K11" s="5"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="4"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="47"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="54"/>
       <c r="K12" s="5"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
@@ -2058,6 +2300,461 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A2:K29"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="3" width="8.42578125" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="25.42578125" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" customWidth="1"/>
+    <col min="11" max="11" width="22.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B2" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B3" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="31">
+        <v>46043</v>
+      </c>
+      <c r="J3" s="31">
+        <v>46043</v>
+      </c>
+      <c r="K3" s="39"/>
+    </row>
+    <row r="4" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="65"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
+    </row>
+    <row r="5" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B5" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="58"/>
+    </row>
+    <row r="6" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B6" s="15">
+        <v>1</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="16"/>
+      <c r="E6" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="16"/>
+      <c r="H6" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" s="15"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="58"/>
+    </row>
+    <row r="7" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B7" s="15">
+        <v>2</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7" s="16"/>
+      <c r="H7" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="72"/>
+      <c r="K7" s="58"/>
+    </row>
+    <row r="8" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B8" s="15">
+        <v>3</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="F8" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="I8" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="72"/>
+      <c r="K8" s="58"/>
+    </row>
+    <row r="9" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B9" s="15">
+        <v>4</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="I9" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="65"/>
+      <c r="K9" s="58"/>
+    </row>
+    <row r="10" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B10" s="15">
+        <v>5</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="15"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="58"/>
+    </row>
+    <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="21"/>
+      <c r="B11" s="15">
+        <v>6</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="15"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="58"/>
+    </row>
+    <row r="12" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="15">
+        <v>7</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="15"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="58"/>
+    </row>
+    <row r="16" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B16" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B17" s="67" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
+    </row>
+    <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
+    </row>
+    <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+    </row>
+    <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
+    </row>
+    <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
+    </row>
+    <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
+    </row>
+    <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
+    </row>
+    <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="68"/>
+    </row>
+    <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="68"/>
+      <c r="K25" s="68"/>
+    </row>
+    <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
+    </row>
+    <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
+    </row>
+    <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
+    </row>
+    <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="B17:K29"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J12:K12"/>
+  </mergeCells>
+  <phoneticPr fontId="11"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{380781A7-B342-4BB6-804B-5CD1699DE04A}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2077,12 +2774,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="58"/>
       <c r="F2" s="15" t="s">
         <v>4</v>
       </c>
@@ -2103,12 +2800,12 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="29" t="s">
         <v>29</v>
       </c>
@@ -2124,21 +2821,21 @@
       <c r="J3" s="31">
         <v>46043</v>
       </c>
-      <c r="K3" s="60"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="4" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="51"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B5" s="18" t="s">
@@ -2165,10 +2862,10 @@
       <c r="I5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="51"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B6" s="15">
@@ -2177,7 +2874,7 @@
       <c r="C6" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="45" t="s">
         <v>48</v>
       </c>
       <c r="E6" s="34" t="s">
@@ -2193,10 +2890,10 @@
       <c r="I6" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="59" t="s">
+      <c r="J6" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="51"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="15">
@@ -2205,7 +2902,7 @@
       <c r="C7" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="45" t="s">
         <v>48</v>
       </c>
       <c r="E7" s="34" t="s">
@@ -2221,8 +2918,8 @@
       <c r="I7" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="58"/>
-      <c r="K7" s="51"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="58"/>
     </row>
     <row r="8" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B8" s="15">
@@ -2235,8 +2932,8 @@
       <c r="G8" s="16"/>
       <c r="H8" s="19"/>
       <c r="I8" s="15"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="51"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="58"/>
     </row>
     <row r="9" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B9" s="15">
@@ -2249,8 +2946,8 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="51"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="58"/>
     </row>
     <row r="10" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B10" s="15">
@@ -2263,8 +2960,8 @@
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
       <c r="I10" s="15"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="51"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="58"/>
     </row>
     <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="21"/>
@@ -2287,162 +2984,162 @@
       </c>
     </row>
     <row r="17" spans="2:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
     </row>
     <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
     </row>
     <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
     </row>
     <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
     </row>
     <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="68"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="68"/>
+      <c r="K25" s="68"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
     </row>
     <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="62"/>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2462,7 +3159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8C0B2B2-3A1F-4DE5-AA2B-7FAF44E2CCE3}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2483,12 +3180,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="58"/>
       <c r="F2" s="15" t="s">
         <v>4</v>
       </c>
@@ -2509,12 +3206,12 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="29" t="s">
         <v>149</v>
       </c>
@@ -2530,21 +3227,21 @@
       <c r="J3" s="31">
         <v>46043</v>
       </c>
-      <c r="K3" s="60"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="4" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="51"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B5" s="18" t="s">
@@ -2571,10 +3268,10 @@
       <c r="I5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="51"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B6" s="15">
@@ -2595,8 +3292,8 @@
         <v>72</v>
       </c>
       <c r="I6" s="15"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="51"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B7" s="15">
@@ -2617,8 +3314,8 @@
       <c r="I7" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="58"/>
-      <c r="K7" s="51"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="58"/>
     </row>
     <row r="8" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B8" s="15">
@@ -2635,14 +3332,14 @@
       <c r="G8" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="H8" s="63" t="s">
+      <c r="H8" s="40" t="s">
         <v>151</v>
       </c>
       <c r="I8" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="58"/>
-      <c r="K8" s="51"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="58"/>
     </row>
     <row r="9" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B9" s="15">
@@ -2665,8 +3362,8 @@
       <c r="I9" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="53"/>
-      <c r="K9" s="51"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="58"/>
     </row>
     <row r="10" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B10" s="15">
@@ -2679,8 +3376,8 @@
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
       <c r="I10" s="15"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="51"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="58"/>
     </row>
     <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="21"/>
@@ -2703,162 +3400,162 @@
       </c>
     </row>
     <row r="17" spans="2:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="74" t="s">
         <v>153</v>
       </c>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="75"/>
+      <c r="H17" s="75"/>
+      <c r="I17" s="75"/>
+      <c r="J17" s="75"/>
+      <c r="K17" s="75"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="69"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="69"/>
-      <c r="J18" s="69"/>
-      <c r="K18" s="69"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="75"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="75"/>
+      <c r="J18" s="75"/>
+      <c r="K18" s="75"/>
     </row>
     <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="69"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="69"/>
-      <c r="J19" s="69"/>
-      <c r="K19" s="69"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="75"/>
+      <c r="G19" s="75"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="75"/>
+      <c r="J19" s="75"/>
+      <c r="K19" s="75"/>
     </row>
     <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="69"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="69"/>
-      <c r="J20" s="69"/>
-      <c r="K20" s="69"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="75"/>
+      <c r="H20" s="75"/>
+      <c r="I20" s="75"/>
+      <c r="J20" s="75"/>
+      <c r="K20" s="75"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="69"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="75"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="75"/>
+      <c r="J21" s="75"/>
+      <c r="K21" s="75"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="75"/>
+      <c r="J22" s="75"/>
+      <c r="K22" s="75"/>
     </row>
     <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="69"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="69"/>
-      <c r="K23" s="69"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
+      <c r="J23" s="75"/>
+      <c r="K23" s="75"/>
     </row>
     <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="69"/>
-      <c r="C24" s="69"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="69"/>
-      <c r="J24" s="69"/>
-      <c r="K24" s="69"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="75"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="75"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="69"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="69"/>
-      <c r="J25" s="69"/>
-      <c r="K25" s="69"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
+      <c r="J25" s="75"/>
+      <c r="K25" s="75"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="69"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="69"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="75"/>
+      <c r="J26" s="75"/>
+      <c r="K26" s="75"/>
     </row>
     <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="69"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="69"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="69"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="75"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="75"/>
+      <c r="F27" s="75"/>
+      <c r="G27" s="75"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="75"/>
+      <c r="J27" s="75"/>
+      <c r="K27" s="75"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="69"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="69"/>
-      <c r="J28" s="69"/>
-      <c r="K28" s="69"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="75"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="75"/>
+      <c r="H28" s="75"/>
+      <c r="I28" s="75"/>
+      <c r="J28" s="75"/>
+      <c r="K28" s="75"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="69"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="69"/>
-      <c r="H29" s="69"/>
-      <c r="I29" s="69"/>
-      <c r="J29" s="69"/>
-      <c r="K29" s="69"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="75"/>
+      <c r="D29" s="75"/>
+      <c r="E29" s="75"/>
+      <c r="F29" s="75"/>
+      <c r="G29" s="75"/>
+      <c r="H29" s="75"/>
+      <c r="I29" s="75"/>
+      <c r="J29" s="75"/>
+      <c r="K29" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2878,7 +3575,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A066251-59C3-412D-9354-FA39F41087D1}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2898,12 +3595,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="58"/>
       <c r="F2" s="15" t="s">
         <v>4</v>
       </c>
@@ -2924,12 +3621,12 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="29" t="s">
         <v>157</v>
       </c>
@@ -2945,21 +3642,21 @@
       <c r="J3" s="31">
         <v>46043</v>
       </c>
-      <c r="K3" s="60"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="4" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="51"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B5" s="18" t="s">
@@ -2986,10 +3683,10 @@
       <c r="I5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="51"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B6" s="15">
@@ -2998,7 +3695,7 @@
       <c r="C6" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="45" t="s">
         <v>48</v>
       </c>
       <c r="E6" s="34" t="s">
@@ -3014,10 +3711,10 @@
       <c r="I6" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="59" t="s">
+      <c r="J6" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="51"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B7" s="15">
@@ -3026,7 +3723,7 @@
       <c r="C7" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="45" t="s">
         <v>48</v>
       </c>
       <c r="E7" s="34" t="s">
@@ -3042,10 +3739,10 @@
       <c r="I7" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="59" t="s">
+      <c r="J7" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="K7" s="51"/>
+      <c r="K7" s="58"/>
     </row>
     <row r="8" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B8" s="15">
@@ -3058,8 +3755,8 @@
       <c r="G8" s="16"/>
       <c r="H8" s="19"/>
       <c r="I8" s="15"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="51"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="58"/>
     </row>
     <row r="9" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B9" s="15">
@@ -3072,8 +3769,8 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="51"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="58"/>
     </row>
     <row r="10" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B10" s="15">
@@ -3086,8 +3783,8 @@
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
       <c r="I10" s="15"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="51"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="58"/>
     </row>
     <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="21"/>
@@ -3110,162 +3807,162 @@
       </c>
     </row>
     <row r="17" spans="2:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
     </row>
     <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
     </row>
     <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
     </row>
     <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
     </row>
     <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="68"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="68"/>
+      <c r="K25" s="68"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
     </row>
     <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="62"/>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3286,6 +3983,617 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F5E2C5-D893-426D-9454-088115873D21}">
+  <dimension ref="A1:R29"/>
+  <sheetFormatPr defaultColWidth="8.140625" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" style="80" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="80" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="80" customWidth="1"/>
+    <col min="4" max="14" width="8.140625" style="80" customWidth="1"/>
+    <col min="15" max="18" width="12.28515625" style="80" customWidth="1"/>
+    <col min="19" max="16384" width="8.140625" style="80"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="76" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="77" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+    </row>
+    <row r="2" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="81">
+        <v>46042</v>
+      </c>
+      <c r="R2" s="79"/>
+    </row>
+    <row r="3" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="82"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+    </row>
+    <row r="4" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="83" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="84" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84" t="s">
+        <v>173</v>
+      </c>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84" t="s">
+        <v>174</v>
+      </c>
+      <c r="J4" s="84"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="84"/>
+      <c r="M4" s="84"/>
+      <c r="N4" s="84"/>
+      <c r="O4" s="84"/>
+      <c r="P4" s="84"/>
+      <c r="Q4" s="84"/>
+      <c r="R4" s="84"/>
+    </row>
+    <row r="5" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="85">
+        <v>1</v>
+      </c>
+      <c r="B5" s="86">
+        <v>46042</v>
+      </c>
+      <c r="C5" s="86"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87" t="s">
+        <v>176</v>
+      </c>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="88" t="s">
+        <v>175</v>
+      </c>
+      <c r="J5" s="88"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="88"/>
+      <c r="M5" s="88"/>
+      <c r="N5" s="88"/>
+      <c r="O5" s="88"/>
+      <c r="P5" s="88"/>
+      <c r="Q5" s="88"/>
+      <c r="R5" s="88"/>
+    </row>
+    <row r="6" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="89">
+        <v>2</v>
+      </c>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="92"/>
+      <c r="K6" s="92"/>
+      <c r="L6" s="92"/>
+      <c r="M6" s="92"/>
+      <c r="N6" s="92"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="92"/>
+      <c r="Q6" s="92"/>
+      <c r="R6" s="92"/>
+    </row>
+    <row r="7" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="89">
+        <v>3</v>
+      </c>
+      <c r="B7" s="90"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="92"/>
+      <c r="K7" s="92"/>
+      <c r="L7" s="92"/>
+      <c r="M7" s="92"/>
+      <c r="N7" s="92"/>
+      <c r="O7" s="92"/>
+      <c r="P7" s="92"/>
+      <c r="Q7" s="92"/>
+      <c r="R7" s="92"/>
+    </row>
+    <row r="8" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="89">
+        <v>4</v>
+      </c>
+      <c r="B8" s="90"/>
+      <c r="C8" s="90"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="92"/>
+      <c r="K8" s="92"/>
+      <c r="L8" s="92"/>
+      <c r="M8" s="92"/>
+      <c r="N8" s="92"/>
+      <c r="O8" s="92"/>
+      <c r="P8" s="92"/>
+      <c r="Q8" s="92"/>
+      <c r="R8" s="92"/>
+    </row>
+    <row r="9" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="89">
+        <v>5</v>
+      </c>
+      <c r="B9" s="90"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="92"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="92"/>
+      <c r="L9" s="92"/>
+      <c r="M9" s="92"/>
+      <c r="N9" s="92"/>
+      <c r="O9" s="92"/>
+      <c r="P9" s="92"/>
+      <c r="Q9" s="92"/>
+      <c r="R9" s="92"/>
+    </row>
+    <row r="10" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="89">
+        <v>6</v>
+      </c>
+      <c r="B10" s="90"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="92"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="92"/>
+      <c r="P10" s="92"/>
+      <c r="Q10" s="92"/>
+      <c r="R10" s="92"/>
+    </row>
+    <row r="11" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="89">
+        <v>7</v>
+      </c>
+      <c r="B11" s="90"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="91"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="92"/>
+      <c r="K11" s="92"/>
+      <c r="L11" s="92"/>
+      <c r="M11" s="92"/>
+      <c r="N11" s="92"/>
+      <c r="O11" s="92"/>
+      <c r="P11" s="92"/>
+      <c r="Q11" s="92"/>
+      <c r="R11" s="92"/>
+    </row>
+    <row r="12" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="89">
+        <v>8</v>
+      </c>
+      <c r="B12" s="90"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="92"/>
+      <c r="K12" s="92"/>
+      <c r="L12" s="92"/>
+      <c r="M12" s="92"/>
+      <c r="N12" s="92"/>
+      <c r="O12" s="92"/>
+      <c r="P12" s="92"/>
+      <c r="Q12" s="92"/>
+      <c r="R12" s="92"/>
+    </row>
+    <row r="13" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="89">
+        <v>9</v>
+      </c>
+      <c r="B13" s="90"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="92"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="92"/>
+      <c r="O13" s="92"/>
+      <c r="P13" s="92"/>
+      <c r="Q13" s="92"/>
+      <c r="R13" s="92"/>
+    </row>
+    <row r="14" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="89">
+        <v>10</v>
+      </c>
+      <c r="B14" s="90"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="91"/>
+      <c r="G14" s="91"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="92"/>
+      <c r="K14" s="92"/>
+      <c r="L14" s="92"/>
+      <c r="M14" s="92"/>
+      <c r="N14" s="92"/>
+      <c r="O14" s="92"/>
+      <c r="P14" s="92"/>
+      <c r="Q14" s="92"/>
+      <c r="R14" s="92"/>
+    </row>
+    <row r="15" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="89">
+        <v>11</v>
+      </c>
+      <c r="B15" s="90"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="91"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="91"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="92"/>
+      <c r="J15" s="92"/>
+      <c r="K15" s="92"/>
+      <c r="L15" s="92"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="92"/>
+      <c r="O15" s="92"/>
+      <c r="P15" s="92"/>
+      <c r="Q15" s="92"/>
+      <c r="R15" s="92"/>
+    </row>
+    <row r="16" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="89">
+        <v>12</v>
+      </c>
+      <c r="B16" s="90"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="91"/>
+      <c r="E16" s="91"/>
+      <c r="F16" s="91"/>
+      <c r="G16" s="91"/>
+      <c r="H16" s="91"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="92"/>
+      <c r="K16" s="92"/>
+      <c r="L16" s="92"/>
+      <c r="M16" s="92"/>
+      <c r="N16" s="92"/>
+      <c r="O16" s="92"/>
+      <c r="P16" s="92"/>
+      <c r="Q16" s="92"/>
+      <c r="R16" s="92"/>
+    </row>
+    <row r="17" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="89">
+        <v>13</v>
+      </c>
+      <c r="B17" s="90"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="91"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="92"/>
+      <c r="J17" s="92"/>
+      <c r="K17" s="92"/>
+      <c r="L17" s="92"/>
+      <c r="M17" s="92"/>
+      <c r="N17" s="92"/>
+      <c r="O17" s="92"/>
+      <c r="P17" s="92"/>
+      <c r="Q17" s="92"/>
+      <c r="R17" s="92"/>
+    </row>
+    <row r="18" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="89">
+        <v>14</v>
+      </c>
+      <c r="B18" s="90"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="91"/>
+      <c r="E18" s="91"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="91"/>
+      <c r="H18" s="91"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="92"/>
+      <c r="K18" s="92"/>
+      <c r="L18" s="92"/>
+      <c r="M18" s="92"/>
+      <c r="N18" s="92"/>
+      <c r="O18" s="92"/>
+      <c r="P18" s="92"/>
+      <c r="Q18" s="92"/>
+      <c r="R18" s="92"/>
+    </row>
+    <row r="19" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="89">
+        <v>15</v>
+      </c>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="91"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="92"/>
+      <c r="L19" s="92"/>
+      <c r="M19" s="92"/>
+      <c r="N19" s="92"/>
+      <c r="O19" s="92"/>
+      <c r="P19" s="92"/>
+      <c r="Q19" s="92"/>
+      <c r="R19" s="92"/>
+    </row>
+    <row r="20" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="89">
+        <v>16</v>
+      </c>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="91"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="91"/>
+      <c r="I20" s="92"/>
+      <c r="J20" s="92"/>
+      <c r="K20" s="92"/>
+      <c r="L20" s="92"/>
+      <c r="M20" s="92"/>
+      <c r="N20" s="92"/>
+      <c r="O20" s="92"/>
+      <c r="P20" s="92"/>
+      <c r="Q20" s="92"/>
+      <c r="R20" s="92"/>
+    </row>
+    <row r="21" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="89">
+        <v>17</v>
+      </c>
+      <c r="B21" s="90"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="91"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="91"/>
+      <c r="I21" s="92"/>
+      <c r="J21" s="92"/>
+      <c r="K21" s="92"/>
+      <c r="L21" s="92"/>
+      <c r="M21" s="92"/>
+      <c r="N21" s="92"/>
+      <c r="O21" s="92"/>
+      <c r="P21" s="92"/>
+      <c r="Q21" s="92"/>
+      <c r="R21" s="92"/>
+    </row>
+    <row r="22" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="89">
+        <v>18</v>
+      </c>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="91"/>
+      <c r="F22" s="91"/>
+      <c r="G22" s="91"/>
+      <c r="H22" s="91"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="92"/>
+      <c r="K22" s="92"/>
+      <c r="L22" s="92"/>
+      <c r="M22" s="92"/>
+      <c r="N22" s="92"/>
+      <c r="O22" s="92"/>
+      <c r="P22" s="92"/>
+      <c r="Q22" s="92"/>
+      <c r="R22" s="92"/>
+    </row>
+    <row r="23" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="80">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:R21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:R22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:R19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:R20"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:R17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:R18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:R15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:R16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:R11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="I12:R12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:R9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:R10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:R7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:R8"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:R5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="I6:R6"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:O2"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:R4"/>
+  </mergeCells>
+  <phoneticPr fontId="11"/>
+  <pageMargins left="0.23611111111111099" right="0.23611111111111099" top="0.31527777777777799" bottom="0.27569444444444402" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3309,15 +4617,15 @@
       <c r="C3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="66" t="s">
+      <c r="D3" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="51"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58"/>
     </row>
     <row r="4" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="12">
@@ -3329,24 +4637,24 @@
       <c r="D4" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="71" t="s">
+      <c r="E4" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="76"/>
-      <c r="J4" s="77" t="s">
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="58"/>
+      <c r="J4" s="55" t="s">
         <v>168</v>
       </c>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="55"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="55"/>
     </row>
     <row r="5" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="12">
@@ -3358,12 +4666,12 @@
       <c r="D5" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="72" t="s">
+      <c r="E5" s="60" t="s">
         <v>159</v>
       </c>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="74"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="62"/>
     </row>
     <row r="6" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="12">
@@ -3375,20 +4683,20 @@
       <c r="D6" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="72" t="s">
+      <c r="E6" s="60" t="s">
         <v>160</v>
       </c>
-      <c r="F6" s="73"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="74"/>
-      <c r="K6" s="48" t="s">
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="62"/>
+      <c r="K6" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="41"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="48"/>
     </row>
     <row r="7" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="12">
@@ -3400,18 +4708,18 @@
       <c r="D7" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="71" t="s">
+      <c r="E7" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="76"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="44"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="58"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="51"/>
     </row>
     <row r="8" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="12">
@@ -3423,18 +4731,18 @@
       <c r="D8" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="E8" s="71" t="s">
+      <c r="E8" s="59" t="s">
         <v>162</v>
       </c>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="76"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="44"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="58"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="50"/>
+      <c r="M8" s="50"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="50"/>
+      <c r="P8" s="51"/>
     </row>
     <row r="9" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="12">
@@ -3446,18 +4754,18 @@
       <c r="D9" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="71" t="s">
+      <c r="E9" s="59" t="s">
         <v>163</v>
       </c>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="76"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
-      <c r="O9" s="43"/>
-      <c r="P9" s="44"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="58"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="50"/>
+      <c r="M9" s="50"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="50"/>
+      <c r="P9" s="51"/>
     </row>
     <row r="10" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="12">
@@ -3469,18 +4777,18 @@
       <c r="D10" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="71" t="s">
+      <c r="E10" s="59" t="s">
         <v>164</v>
       </c>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="76"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="43"/>
-      <c r="P10" s="44"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="58"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="50"/>
+      <c r="P10" s="51"/>
     </row>
     <row r="11" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="12">
@@ -3492,18 +4800,18 @@
       <c r="D11" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="71" t="s">
+      <c r="E11" s="59" t="s">
         <v>165</v>
       </c>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="76"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="43"/>
-      <c r="P11" s="44"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="58"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="50"/>
+      <c r="M11" s="50"/>
+      <c r="N11" s="50"/>
+      <c r="O11" s="50"/>
+      <c r="P11" s="51"/>
     </row>
     <row r="12" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="12">
@@ -3515,18 +4823,18 @@
       <c r="D12" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="72" t="s">
+      <c r="E12" s="60" t="s">
         <v>166</v>
       </c>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="74"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="44"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="62"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="51"/>
     </row>
     <row r="13" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="12">
@@ -3538,18 +4846,18 @@
       <c r="D13" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="71" t="s">
+      <c r="E13" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="76"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="47"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="58"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="53"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="53"/>
+      <c r="P13" s="54"/>
     </row>
     <row r="14" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="12">
@@ -3557,10 +4865,10 @@
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="13"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="75"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="76"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="58"/>
     </row>
     <row r="15" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="12">
@@ -3568,16 +4876,16 @@
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="13"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="75"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="76"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="58"/>
     </row>
     <row r="16" spans="2:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -3616,7 +4924,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3636,12 +4944,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="58"/>
       <c r="F2" s="15" t="s">
         <v>4</v>
       </c>
@@ -3662,12 +4970,12 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="29" t="s">
         <v>20</v>
       </c>
@@ -3689,15 +4997,15 @@
       <c r="B4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="51"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B5" s="18" t="s">
@@ -3724,10 +5032,10 @@
       <c r="I5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="51"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B6" s="15">
@@ -3750,8 +5058,8 @@
       <c r="I6" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="58"/>
-      <c r="K6" s="51"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B7" s="15">
@@ -3772,8 +5080,8 @@
       <c r="I7" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="58"/>
-      <c r="K7" s="51"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="58"/>
     </row>
     <row r="8" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B8" s="15">
@@ -3794,10 +5102,10 @@
       <c r="I8" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="59" t="s">
+      <c r="J8" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="K8" s="51"/>
+      <c r="K8" s="58"/>
     </row>
     <row r="9" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B9" s="15">
@@ -3818,8 +5126,8 @@
       <c r="I9" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="53"/>
-      <c r="K9" s="51"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="58"/>
     </row>
     <row r="10" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B10" s="15">
@@ -3840,8 +5148,8 @@
         <v>57</v>
       </c>
       <c r="I10" s="15"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="51"/>
+      <c r="J10" s="66"/>
+      <c r="K10" s="58"/>
     </row>
     <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="21"/>
@@ -3863,8 +5171,8 @@
         <v>57</v>
       </c>
       <c r="I11" s="15"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="51"/>
+      <c r="J11" s="66"/>
+      <c r="K11" s="58"/>
     </row>
     <row r="12" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="15">
@@ -3887,8 +5195,8 @@
       <c r="I12" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J12" s="53"/>
-      <c r="K12" s="51"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="58"/>
     </row>
     <row r="16" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B16" s="7" t="s">
@@ -3896,162 +5204,162 @@
       </c>
     </row>
     <row r="17" spans="2:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
     </row>
     <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
     </row>
     <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
     </row>
     <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
     </row>
     <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="68"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="68"/>
+      <c r="K25" s="68"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
     </row>
     <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="62"/>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -4073,7 +5381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0D348A-CD29-49F3-8733-1C653A7E96D5}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4093,12 +5401,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="58"/>
       <c r="F2" s="15" t="s">
         <v>4</v>
       </c>
@@ -4119,12 +5427,12 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="29" t="s">
         <v>21</v>
       </c>
@@ -4140,21 +5448,21 @@
       <c r="J3" s="31">
         <v>46043</v>
       </c>
-      <c r="K3" s="60"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="4" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="51"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B5" s="18" t="s">
@@ -4181,10 +5489,10 @@
       <c r="I5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="51"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B6" s="15">
@@ -4197,7 +5505,7 @@
       <c r="E6" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="64" t="s">
+      <c r="F6" s="41" t="s">
         <v>79</v>
       </c>
       <c r="G6" s="16"/>
@@ -4207,8 +5515,8 @@
       <c r="I6" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="58"/>
-      <c r="K6" s="51"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B7" s="15">
@@ -4229,10 +5537,10 @@
       <c r="I7" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="59" t="s">
+      <c r="J7" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="K7" s="51"/>
+      <c r="K7" s="58"/>
     </row>
     <row r="8" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B8" s="15">
@@ -4249,14 +5557,14 @@
       <c r="G8" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="H8" s="63" t="s">
+      <c r="H8" s="40" t="s">
         <v>59</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="58"/>
-      <c r="K8" s="51"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="58"/>
     </row>
     <row r="9" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B9" s="15">
@@ -4269,8 +5577,8 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="51"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="58"/>
     </row>
     <row r="10" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B10" s="15">
@@ -4283,8 +5591,8 @@
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
       <c r="I10" s="15"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="51"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="58"/>
     </row>
     <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="21"/>
@@ -4307,162 +5615,162 @@
       </c>
     </row>
     <row r="17" spans="2:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
     </row>
     <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
     </row>
     <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
     </row>
     <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
     </row>
     <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="68"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="68"/>
+      <c r="K25" s="68"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
     </row>
     <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="62"/>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4482,7 +5790,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74BBF7FB-34CE-4F1A-BB1E-E42DCB5FBFEA}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4503,12 +5811,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="58"/>
       <c r="F2" s="15" t="s">
         <v>4</v>
       </c>
@@ -4529,12 +5837,12 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="29" t="s">
         <v>22</v>
       </c>
@@ -4550,21 +5858,21 @@
       <c r="J3" s="31">
         <v>46043</v>
       </c>
-      <c r="K3" s="60"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="4" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="51"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B5" s="18" t="s">
@@ -4591,10 +5899,10 @@
       <c r="I5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="51"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B6" s="15">
@@ -4617,8 +5925,8 @@
       <c r="I6" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="58"/>
-      <c r="K6" s="51"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B7" s="15">
@@ -4641,10 +5949,10 @@
       <c r="I7" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="59" t="s">
+      <c r="J7" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="K7" s="51"/>
+      <c r="K7" s="58"/>
     </row>
     <row r="8" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B8" s="15">
@@ -4659,14 +5967,14 @@
         <v>81</v>
       </c>
       <c r="G8" s="16"/>
-      <c r="H8" s="63" t="s">
+      <c r="H8" s="40" t="s">
         <v>54</v>
       </c>
       <c r="I8" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="58"/>
-      <c r="K8" s="51"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="58"/>
     </row>
     <row r="9" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B9" s="15">
@@ -4687,8 +5995,8 @@
       <c r="I9" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="53"/>
-      <c r="K9" s="51"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="58"/>
     </row>
     <row r="10" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B10" s="15">
@@ -4701,8 +6009,8 @@
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
       <c r="I10" s="15"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="51"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="58"/>
     </row>
     <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="21"/>
@@ -4725,162 +6033,162 @@
       </c>
     </row>
     <row r="17" spans="2:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
     </row>
     <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
     </row>
     <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
     </row>
     <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
     </row>
     <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="68"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="68"/>
+      <c r="K25" s="68"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
     </row>
     <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="62"/>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4900,7 +6208,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4921,12 +6229,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="58"/>
       <c r="F2" s="15" t="s">
         <v>4</v>
       </c>
@@ -4947,12 +6255,12 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="29" t="s">
         <v>23</v>
       </c>
@@ -4968,21 +6276,21 @@
       <c r="J3" s="31">
         <v>46043</v>
       </c>
-      <c r="K3" s="60"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="4" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="51"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B5" s="18" t="s">
@@ -5009,10 +6317,10 @@
       <c r="I5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="51"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B6" s="15">
@@ -5035,8 +6343,8 @@
       <c r="I6" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="58"/>
-      <c r="K6" s="51"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B7" s="15">
@@ -5059,10 +6367,10 @@
       <c r="I7" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="59" t="s">
+      <c r="J7" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="K7" s="51"/>
+      <c r="K7" s="58"/>
     </row>
     <row r="8" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B8" s="15">
@@ -5079,14 +6387,14 @@
         <v>80</v>
       </c>
       <c r="G8" s="16"/>
-      <c r="H8" s="63" t="s">
+      <c r="H8" s="40" t="s">
         <v>83</v>
       </c>
       <c r="I8" s="15"/>
-      <c r="J8" s="59" t="s">
+      <c r="J8" s="73" t="s">
         <v>100</v>
       </c>
-      <c r="K8" s="51"/>
+      <c r="K8" s="58"/>
     </row>
     <row r="9" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B9" s="15">
@@ -5105,8 +6413,8 @@
         <v>98</v>
       </c>
       <c r="I9" s="15"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="51"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="58"/>
     </row>
     <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B10" s="15">
@@ -5120,7 +6428,7 @@
       <c r="F10" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="65" t="s">
+      <c r="G10" s="42" t="s">
         <v>97</v>
       </c>
       <c r="H10" s="34" t="s">
@@ -5129,8 +6437,8 @@
       <c r="I10" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="53"/>
-      <c r="K10" s="51"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="58"/>
     </row>
     <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="21"/>
@@ -5154,8 +6462,8 @@
       <c r="I11" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J11" s="53"/>
-      <c r="K11" s="51"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="58"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="15">
@@ -5178,8 +6486,8 @@
       <c r="I12" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J12" s="53"/>
-      <c r="K12" s="51"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="58"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="15">
@@ -5202,8 +6510,8 @@
       <c r="I13" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J13" s="53"/>
-      <c r="K13" s="51"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="58"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="15">
@@ -5216,8 +6524,8 @@
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
       <c r="I14" s="15"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="51"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="58"/>
     </row>
     <row r="16" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B16" s="7" t="s">
@@ -5225,162 +6533,162 @@
       </c>
     </row>
     <row r="17" spans="2:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
     </row>
     <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
     </row>
     <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
     </row>
     <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
     </row>
     <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="68"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="68"/>
+      <c r="K25" s="68"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
     </row>
     <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="62"/>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -5404,7 +6712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B53E9EED-06CB-4767-9208-BF73E40CF5FA}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -5424,12 +6732,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="58"/>
       <c r="F2" s="15" t="s">
         <v>4</v>
       </c>
@@ -5450,12 +6758,12 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="29" t="s">
         <v>24</v>
       </c>
@@ -5471,21 +6779,21 @@
       <c r="J3" s="31">
         <v>46043</v>
       </c>
-      <c r="K3" s="60"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="4" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="51"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B5" s="18" t="s">
@@ -5512,10 +6820,10 @@
       <c r="I5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="51"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B6" s="15">
@@ -5538,8 +6846,8 @@
       <c r="I6" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="58"/>
-      <c r="K6" s="51"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B7" s="15">
@@ -5552,7 +6860,7 @@
       <c r="E7" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="F7" s="67" t="s">
+      <c r="F7" s="44" t="s">
         <v>105</v>
       </c>
       <c r="G7" s="16"/>
@@ -5562,10 +6870,10 @@
       <c r="I7" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="59" t="s">
+      <c r="J7" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="K7" s="51"/>
+      <c r="K7" s="58"/>
     </row>
     <row r="8" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B8" s="15">
@@ -5581,19 +6889,19 @@
       <c r="F8" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="G8" s="67" t="s">
+      <c r="G8" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="H8" s="63" t="s">
+      <c r="H8" s="40" t="s">
         <v>56</v>
       </c>
       <c r="I8" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="59" t="s">
+      <c r="J8" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="K8" s="51"/>
+      <c r="K8" s="58"/>
     </row>
     <row r="9" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B9" s="15">
@@ -5616,8 +6924,8 @@
       <c r="I9" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="53"/>
-      <c r="K9" s="51"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="58"/>
     </row>
     <row r="10" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B10" s="15">
@@ -5628,7 +6936,7 @@
       <c r="E10" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="64" t="s">
+      <c r="F10" s="41" t="s">
         <v>109</v>
       </c>
       <c r="G10" s="34" t="s">
@@ -5638,8 +6946,8 @@
         <v>57</v>
       </c>
       <c r="I10" s="15"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="51"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="58"/>
     </row>
     <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="21"/>
@@ -5651,7 +6959,7 @@
       <c r="E11" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="64" t="s">
+      <c r="F11" s="41" t="s">
         <v>110</v>
       </c>
       <c r="G11" s="34" t="s">
@@ -5661,8 +6969,8 @@
         <v>57</v>
       </c>
       <c r="I11" s="15"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="51"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="58"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="15">
@@ -5675,8 +6983,8 @@
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
       <c r="I12" s="15"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="51"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="58"/>
     </row>
     <row r="16" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B16" s="7" t="s">
@@ -5684,162 +6992,162 @@
       </c>
     </row>
     <row r="17" spans="2:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
     </row>
     <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
     </row>
     <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
     </row>
     <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
     </row>
     <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="68"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="68"/>
+      <c r="K25" s="68"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
     </row>
     <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="62"/>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -5861,7 +7169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{592EE3BF-603F-47A9-8FFC-E9437E0394A1}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -5881,12 +7189,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="58"/>
       <c r="F2" s="15" t="s">
         <v>4</v>
       </c>
@@ -5907,12 +7215,12 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="29" t="s">
         <v>25</v>
       </c>
@@ -5928,21 +7236,21 @@
       <c r="J3" s="31">
         <v>46043</v>
       </c>
-      <c r="K3" s="60"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="4" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="51"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B5" s="18" t="s">
@@ -5969,10 +7277,10 @@
       <c r="I5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="51"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B6" s="15">
@@ -5995,8 +7303,8 @@
       <c r="I6" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="58"/>
-      <c r="K6" s="51"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B7" s="15">
@@ -6019,10 +7327,10 @@
       <c r="I7" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="59" t="s">
+      <c r="J7" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="K7" s="51"/>
+      <c r="K7" s="58"/>
     </row>
     <row r="8" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B8" s="15">
@@ -6045,10 +7353,10 @@
       <c r="I8" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="59" t="s">
+      <c r="J8" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="K8" s="51"/>
+      <c r="K8" s="58"/>
     </row>
     <row r="9" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B9" s="15">
@@ -6069,10 +7377,10 @@
         <v>83</v>
       </c>
       <c r="I9" s="15"/>
-      <c r="J9" s="54" t="s">
+      <c r="J9" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="K9" s="51"/>
+      <c r="K9" s="58"/>
     </row>
     <row r="10" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B10" s="15">
@@ -6091,8 +7399,8 @@
         <v>98</v>
       </c>
       <c r="I10" s="15"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="51"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="58"/>
     </row>
     <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="21"/>
@@ -6115,162 +7423,162 @@
       </c>
     </row>
     <row r="17" spans="2:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
     </row>
     <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
     </row>
     <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
     </row>
     <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
     </row>
     <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="68"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="68"/>
+      <c r="K25" s="68"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
     </row>
     <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="62"/>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6288,459 +7596,4 @@
   <phoneticPr fontId="11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A2:K29"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
-    <col min="2" max="3" width="8.42578125" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
-    <col min="7" max="7" width="25.42578125" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" customWidth="1"/>
-    <col min="11" max="11" width="22.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B3" s="56" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>124</v>
-      </c>
-      <c r="H3" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="31">
-        <v>46043</v>
-      </c>
-      <c r="J3" s="31">
-        <v>46043</v>
-      </c>
-      <c r="K3" s="60"/>
-    </row>
-    <row r="4" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B4" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="51"/>
-    </row>
-    <row r="5" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B5" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="57" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="51"/>
-    </row>
-    <row r="6" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B6" s="15">
-        <v>1</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="51"/>
-    </row>
-    <row r="7" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B7" s="15">
-        <v>2</v>
-      </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="F7" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="58"/>
-      <c r="K7" s="51"/>
-    </row>
-    <row r="8" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B8" s="15">
-        <v>3</v>
-      </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="F8" s="37" t="s">
-        <v>129</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="58"/>
-      <c r="K8" s="51"/>
-    </row>
-    <row r="9" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B9" s="15">
-        <v>4</v>
-      </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="F9" s="37" t="s">
-        <v>130</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="I9" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="53"/>
-      <c r="K9" s="51"/>
-    </row>
-    <row r="10" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B10" s="15">
-        <v>5</v>
-      </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>131</v>
-      </c>
-      <c r="G10" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="51"/>
-    </row>
-    <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
-      <c r="B11" s="15">
-        <v>6</v>
-      </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="51"/>
-    </row>
-    <row r="12" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="15">
-        <v>7</v>
-      </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="51"/>
-    </row>
-    <row r="16" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B16" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B17" s="61" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
-    </row>
-    <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
-    </row>
-    <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
-    </row>
-    <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
-    </row>
-    <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
-    </row>
-    <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
-    </row>
-    <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
-    </row>
-    <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
-    </row>
-    <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
-    </row>
-    <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
-    </row>
-    <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
-    </row>
-    <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
-    </row>
-    <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="62"/>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="B17:K29"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J12:K12"/>
-  </mergeCells>
-  <phoneticPr fontId="11"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>